--- a/veterinarian_forms/005_detection_dog_daily_training_record_form--veterinarian_forms.xlsx
+++ b/veterinarian_forms/005_detection_dog_daily_training_record_form--veterinarian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -937,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'obedience'}</t>
+          <t>obedience</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Obedience'}</t>
+          <t>Obedience</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'protection'}</t>
+          <t>protection</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Protection'}</t>
+          <t>Protection</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tracking'}</t>
+          <t>tracking</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Tracking'}</t>
+          <t>Tracking</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'advance'}</t>
+          <t>advance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Advance'}</t>
+          <t>Advance</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'harness'}</t>
+          <t>harness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Harness'}</t>
+          <t>Harness</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'leash'}</t>
+          <t>leash</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Leash'}</t>
+          <t>Leash</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ball'}</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Ball'}</t>
+          <t>Ball</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'clicker'}</t>
+          <t>clicker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Clicker'}</t>
+          <t>Clicker</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'target_stick'}</t>
+          <t>target_stick</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Target stick'}</t>
+          <t>Target stick</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'treats'}</t>
+          <t>treats</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Treats'}</t>
+          <t>Treats</t>
         </is>
       </c>
     </row>
@@ -1174,29 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Other (please specify)'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>equipment_used_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_8,_'label':_'other_(please_specify)'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 8, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
